--- a/daily_matches/job_matches_2026-08-04.xlsx
+++ b/daily_matches/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Microsoft Power BI Technical Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fort Walton Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Redshift, Synapse, Data Lake, Kinesis, MLflow, CI/CD, Jenkins</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Glue, Redshift, Apache Airflow, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4eb0dda56977ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=3534e706b87d7dd9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>Sr. Software Engineer - Core Automation Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, Docker</t>
+          <t>Generative AI, LangChain, RAG, FAISS, Pinecone, S3, Kinesis, FastAPI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5680d993aab0f3e</t>
+          <t>https://www.indeed.com/viewjob?jk=28bf6b38805dd8f3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist / AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LG Electronics</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, BigQuery, FastAPI, Docker, CI/CD</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Apache Airflow, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b69a586c1a7db9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8998c39a2d3607c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41ec093c0ab2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=3979f6a95251946e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer – AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Redshift, Kinesis, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RAG, S3, Glue, Redshift, BigQuery, Data Lake, Apache Airflow, Snowflake, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,172 +636,172 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102b1b66407c2d63</t>
+          <t>https://www.indeed.com/viewjob?jk=f815db0ed6fad5a7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Core Automation Platform</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, FAISS, Pinecone, S3, Kinesis, FastAPI, CI/CD, Jenkins</t>
+          <t>S3, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acacc051b98d38c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b54a93247862959</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Decision Intelligence Engineer (NBA)</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Copilot, MLflow, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
+          <t>S3, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5481fab123fdbe26</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd2758d5ca0ec5c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Redshift, Kinesis, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>S3, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf4c231be457587</t>
+          <t>https://www.indeed.com/viewjob?jk=bbfcb2f3ee241772</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Senior DevOps Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>S3, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98ed69c09171fc2</t>
+          <t>https://www.indeed.com/viewjob?jk=186db7398aa31f15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Practicing Solution Architect</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, Terraform, BigQuery, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa646fe0139ad52</t>
+          <t>https://www.indeed.com/viewjob?jk=36604cce838968ed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>Data Scientist, Redshift, BigQuery, Synapse, Data Lake, Snowflake, Databricks, BigQuery, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7916ae467b0427c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d195c2d700ef8f1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Agentic AI &amp; Vertex AI</t>
+          <t>Sr Data Analyst - Planning &amp; Inventory Management</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, Python, SQL</t>
+          <t>Generative AI, RAG, Prompt Engineering, BigQuery, Git, BigQuery, Hadoop, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5da07ea9415038e4</t>
+          <t>https://www.indeed.com/viewjob?jk=56d647741c3e170c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Agentic AI &amp; Vertex AI</t>
+          <t>Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DraftKings</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, Python, SQL</t>
+          <t>RAG, Copilot, Kubernetes, Terraform, Git, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f158032216cc1261</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f9345b591995c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Data Solutions Engineer</t>
+          <t>DevSecOps Engineer II - SaaS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Synapse, Data Lake, CI/CD, Git, Databricks, Power BI, Python</t>
+          <t>RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Power BI, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b404d89883ee5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=677d7def53db7fac</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Entry-Level Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Birlasoft</t>
+          <t>Pariveda</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Mistral, Prompt Engineering, Databricks, Python</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Terraform, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7967600696016231</t>
+          <t>https://www.indeed.com/viewjob?jk=8afca42f98836dfe</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Entry-Level Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pariveda</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Terraform, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31872c8b26f562e3</t>
+          <t>https://www.indeed.com/viewjob?jk=0fe0d0ea35aeb7d0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Entry-Level Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pariveda</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Terraform, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d0311822cd0b6fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f46373befca890</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NLP AI Engineer</t>
+          <t>Entry-Level Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pariveda</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, PyTorch, Docker, Kubernetes, Python, R</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Terraform, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c89e58d3d390f2</t>
+          <t>https://www.indeed.com/viewjob?jk=17975b745a0d54b3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Entry-Level Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pariveda</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Terraform, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f22e872cda096bd</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb87cf104c0e3eb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Conversational AI Engineer</t>
+          <t>Entry-Level Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pariveda</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, Kubernetes, CI/CD, Python</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Terraform, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=737762e7fffba25b</t>
+          <t>https://www.indeed.com/viewjob?jk=51f146251a74eb7a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>Entry-Level Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Pariveda</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, MySQL, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Terraform, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a17f484512b46ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a6912359bafebc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>Entry-Level Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Pariveda</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, MySQL, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Terraform, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49cb065dcdefa8ef</t>
+          <t>https://www.indeed.com/viewjob?jk=e2fff84c836d89a0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Java</t>
+          <t>Entry-Level Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Pariveda</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, MySQL, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Terraform, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82c3cca6edd87cef</t>
+          <t>https://www.indeed.com/viewjob?jk=688b144c02a2fbd7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>WellSky</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f2b62d5373727f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b57dc4253d0704f1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AAA Life Insurance Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4ca139b5ce94a22</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8bec2bcea26c8e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Senior Specialty Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f024c7e74dd527d0</t>
+          <t>https://www.indeed.com/viewjob?jk=36e33816fc98fd1c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Specialty Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b93d7ce229e42e</t>
+          <t>https://www.indeed.com/viewjob?jk=580d736c7f11946f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Analytics &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BH Management Services, LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, CI/CD, Snowflake, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cdffe5b205f188</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5bd023145300cf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Solutions Architect, Media and Broadcasting</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
+          <t>RAG, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc2cef2275356754</t>
+          <t>https://www.indeed.com/viewjob?jk=a03574605c9e38ea</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Senior Data Scientist, Applied ML</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, MLflow, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6468a261c686526f</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5ee504562a26cb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior .NET Solutions Developer</t>
+          <t>Sr.Security ML / AI Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Prompt Engineering, PyTorch, AWS SageMaker, Data Lake, CI/CD, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,54 +1546,54 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33bfd2f8feede8b</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcaed18f8126328</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358a9f3009b11385</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0428ef7a215e4c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Software Engineer Graduate Intern</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1602,38 +1602,38 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Jenkins, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2e45862a9a566d</t>
+          <t>https://www.indeed.com/viewjob?jk=10efc5d7b3f0485f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Systems Operations Engineer</t>
+          <t>Senior Software Engineer, Capital Markets Technology</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Snowflake, Hadoop, PostgreSQL, Tableau, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91a29c210e011991</t>
+          <t>https://www.indeed.com/viewjob?jk=4b8d7e073d89f13a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Systems Operations Engineer</t>
+          <t>Senior AI Systems Performance Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>External SambaNova Systems</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, LLaMA, TensorFlow, PyTorch, Dataflow, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a129403b06ad9ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=83d6a1862f101419</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Systems Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Databricks, PySpark, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9569a42d9c4634</t>
+          <t>https://www.indeed.com/viewjob?jk=30ae8ee72da7a8a9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Systems Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Databricks, PySpark, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1125783651e89b25</t>
+          <t>https://www.indeed.com/viewjob?jk=457c491bda9105f5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>Algorithm Engineer (Image Processing/Computer Vision)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CaterTrax, Inc.</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25fbe3d303a21a2</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb82251095f146f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Site Reliability Engineer , Engineering Enablement (Remote)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Azure ML, Synapse, Data Lake, GitHub Actions, Git, R, Scala, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15e83d6bfe506b2</t>
+          <t>https://www.indeed.com/viewjob?jk=fa53eb6a6f75ecd4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, Git, MySQL, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>RAG, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0f689bfea9b199</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f0a9d68f6d81</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Front-End Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>BRMi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb9c04c2c72e8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=1c11032f20d5f1f9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>SDET</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38048ba50b2a7b19</t>
+          <t>https://www.indeed.com/viewjob?jk=9be86adb71cea3c2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Tooling Engineer</t>
+          <t>Senior Salesforce Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, S3, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faeff0bc471d69b6</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe39e1b824cd76a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Senior Salesforce Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Rancho Belago, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, S3, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e966c345a42f20f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c0839d3c31dc463c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Specialist - Software Engineering</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
+          <t>RAG, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce5094569161e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=db2a6924c161efb9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
+          <t>RAG, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5db52dc883e06e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f5df1c8cb9bfd9a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Quality Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>National Interstate</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, SQL, R</t>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67e088e94f8a0d79</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8897144ba5a1e9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Quality Engineer</t>
+          <t>E2E Data and Analytics Specialist (175292)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>National Interstate</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richfield, OH, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, SQL, R</t>
+          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,322 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26eb0901c712d272</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Research Engineer Graduate (Monetization Technology - Business Integrity) - 2027 Start (PhD)</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fd29bfa1f3d8dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Senior Consultant II – AI/ML Engineer (.NET Focus) - National General</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>National General Insurance</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee564702f92b8aec</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Machine Learning Modeling Engineer , Cell Manufacturing</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Tesla</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Fremont, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74e4bd4af03a348f</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Research Engineer Graduate (Monetization Technology - Business Integrity) - 2027 Start</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4194b8f23075dfc</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Research Engineer Intern (Monetization Technology - Business Integrity) - 2027 Summer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b231465bbeec686c</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Research Engineer Intern (Monetization Technology - Business Integrity) - 2027 Start (PhD)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75fa736d587d74ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Software Engineer I, Generative AI Applications</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Robert Half</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0dabd133d541b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Software Engineer II (Java/AWS)</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, CI/CD, Git, Cassandra, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b049c5f8d9cf7f13</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Platform Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Everpure</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d64c6701c60f6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c278d4172f12b7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-04.xlsx
+++ b/daily_matches/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kinesis, Kubernetes, CI/CD, Terraform, Git, Snowflake, PySpark</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a167e7c74c87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Software Engineer Graduate (TikTok-PGC-Digital Content Center) - 2027 Start</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New York Post</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, Git, Kafka, MySQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76e43ef1f5bbfd7</t>
+          <t>https://www.indeed.com/viewjob?jk=4d22af308ad0bf59</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Microservices/AWS)</t>
+          <t>Data Scientist 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Jenkins, Terraform, Git, Redshift</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, NoSQL, Dask, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28bcf22a9ef154fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c944fb920be6412e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Perception Validation Engineer</t>
+          <t>Backend Engineer Graduate (User Growth) - 2027 Start</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PlusAI</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, Data Lake, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, MySQL, MongoDB, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f695b1026950547b</t>
+          <t>https://www.indeed.com/viewjob?jk=0596992fe0b17c96</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineers – AI &amp; Agentic Engineering</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>EMCOR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>Norwalk, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Kafka</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b47a4257c438ad</t>
+          <t>https://www.indeed.com/viewjob?jk=49796963804a9fbc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Healthcare Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rapid Eagle Inc</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL</t>
+          <t>Data Scientist, RAG, Data Lake, Databricks, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3eab0da2298e6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Power BI Developer &amp; Data Analyst</t>
+          <t>Sr Cloud Applications Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cornerstone Advisors</t>
+          <t>HealthEquity Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, AKS, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,322 +706,182 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e2964ae230695c</t>
+          <t>https://www.indeed.com/viewjob?jk=bae92fb7eaa8dedc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>System Engineer II NA</t>
+          <t>Machine Learning Engineer Graduate (Brand Ads) - 2027 Start</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3728033321b00995</t>
+          <t>https://www.indeed.com/viewjob?jk=bf4e3c1562d6183a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gravitee.io</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
+          <t>Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73e1b81a95f4cd96</t>
+          <t>https://www.indeed.com/viewjob?jk=1b29ef1c7c191aa5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Scientist</t>
+          <t>Senior Consultant – Data Strategy &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Torq Consulting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Git, Hadoop, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca0fa649ef63d68a</t>
+          <t>https://www.indeed.com/viewjob?jk=c74856c3a868a08d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer Intern (Ads Signal &amp; Measurement) - 2027 Summer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75847a08a282e5dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b2f9a1ca8038f043</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Web Application Developer - Union City, GA</t>
+          <t>Machine Learning Engineer Graduate (Ads Signal &amp; Measurement) - 2027 Start</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GXO Logistics</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Union City, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BigQuery, BigQuery, Tableau, MicroStrategy, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6664a9950764f8e</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Scientist 1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Case Western Reserve University</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Scientist, Data Lake, Git, Databricks, Tableau, Python, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3747a475529bc5</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64db48abe5b7a0e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sr. Application Engineer (DevOps, AI)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>The Seattle Times</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d59598ce14ca437d</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Tooling Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e9e8114abbf943</t>
+          <t>https://www.indeed.com/viewjob?jk=0ed54b2c376ac526</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-04.xlsx
+++ b/daily_matches/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer Graduate (Monetization Data) - 2027 Start</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, Hadoop</t>
+          <t>RAG, S3, Glue, Redshift, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56be91a8f59c7b8c</t>
+          <t>https://www.indeed.com/viewjob?jk=14267222251f75ec</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Backend Software Engineer Graduate (TikTok-PGC-Digital Content Center) - 2027 Start</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, Git, Kafka, MySQL, MongoDB, NoSQL, SQL</t>
+          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d22af308ad0bf59</t>
+          <t>https://www.indeed.com/viewjob?jk=a83abef82bfb222c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist 1</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, NoSQL, Dask, Matplotlib, Seaborn, Python</t>
+          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c944fb920be6412e</t>
+          <t>https://www.indeed.com/viewjob?jk=b36276b09ab0b93d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Backend Engineer Graduate (User Growth) - 2027 Start</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, MySQL, MongoDB, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,94 +601,94 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0596992fe0b17c96</t>
+          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Solutions Integration Engineer IV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EMCOR</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norwalk, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Java</t>
+          <t>RAG, Prompt Engineering, Git, Kafka, NoSQL, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49796963804a9fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d3ae94d02ca0b5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Implementation Engineer (Forward Deployed)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Reveal-Brainspace</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Databricks, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b696b843bec14c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed7b2e0c1de49cd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Cloud Applications Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HealthEquity Inc.</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, AKS, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae92fb7eaa8dedc</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Graduate (Brand Ads) - 2027 Start</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Cellebrite</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, PyTorch, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,147 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf4e3c1562d6183a</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AI DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NiCE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sandy, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b29ef1c7c191aa5</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Consultant – Data Strategy &amp; AI Enablement</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Torq Consulting</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c74856c3a868a08d</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer Intern (Ads Signal &amp; Measurement) - 2027 Summer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2f9a1ca8038f043</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer Graduate (Ads Signal &amp; Measurement) - 2027 Start</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ed54b2c376ac526</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6a6d3d2e92eac9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-04.xlsx
+++ b/daily_matches/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Dremio</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Redshift, BigQuery, Synapse, Data Lake, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14267222251f75ec</t>
+          <t>https://www.indeed.com/viewjob?jk=aab2a218af47694f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>HireBrick</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MongoDB</t>
+          <t>Data Scientist, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, XGBoost, S3, EC2, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83abef82bfb222c</t>
+          <t>https://www.indeed.com/viewjob?jk=42952c6c6822c7d1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Technical Solutions Architect II -- Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MongoDB</t>
+          <t>RAG, Copilot, Cortex, AWS SageMaker, Redshift, BigQuery, Synapse, Apache Airflow, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36276b09ab0b93d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c1844de534a454d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Gen AI Engineer - Generative AI Engineer - W2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>Teamware Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaadae20b9bb3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=91f54a866bb4415f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Solutions Integration Engineer IV</t>
+          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Git, Kafka, NoSQL, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, Docker, Kubernetes, CI/CD, Git, Kafka, Power BI, Matplotlib</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d3ae94d02ca0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Implementation Engineer (Forward Deployed)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Reveal-Brainspace</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Kinesis, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed7b2e0c1de49cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6766bf8c1056e06a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Digital Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a5df0d2ea71619</t>
+          <t>https://www.indeed.com/viewjob?jk=e96a2863adf9faa0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cellebrite</t>
+          <t>HireBrick</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,21 +727,826 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, MLflow, FastAPI, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89871434f1e9543a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jack Henry &amp; Associates</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jack Henry &amp; Associates</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Troy, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jack Henry &amp; Associates</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jack Henry &amp; Associates</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jack Henry &amp; Associates</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Branson, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jack Henry &amp; Associates</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Elizabethtown, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer -W2/1099</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RSA Tech Group</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, LLaMA, Gemini, Prompt Engineering, S3, Redshift, Terraform, Redshift, Python</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a406f8fe296870d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Highlands Ranch, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eec5f74553bd33ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Associate Engineer, Site Reliability</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Verint Systems Inc.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9358a51aac56a77b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Integration Platform Developer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22f587e12fdff403</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Edge</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Kafka, PostgreSQL, MySQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=369dafbf8f945cbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Edge</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Kafka, PostgreSQL, MySQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e7526d8ca2a1f2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer I, MLOps (Python/Big Data)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PNC Financial Services Group</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, AWS SageMaker, PySpark, Kafka, Hadoop, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=917730a7c5496e21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sr. Analyst, Analytics Consulting</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TransUnion</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afda3fdd466fc58e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Architect - GTM Systems</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Samsara</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f141c28a8188c378</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Java Developer (Java-focused)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mobilunity</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AI Engineer, PyTorch, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6a6d3d2e92eac9</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Docker, CI/CD, Kafka, MySQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=966da7da9f101b1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mule ESB Developer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=794eb6cc5b859c21</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OpenShift Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI QA Engineer / AI Test Architect</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Togal AI</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f23e1d27ba11b6f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IT Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t1 energy</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3058ed29473a19b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Henry Ford Health</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, CI/CD, Git, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29388890120f69b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sr. Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, MLflow, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a75cedf85fed51d</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fulton Bank</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61d32392e1cd7f4a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-04.xlsx
+++ b/daily_matches/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer Dremio</t>
+          <t>Technical Architect - Platform - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Redshift, BigQuery, Synapse, Data Lake, Kubernetes, CI/CD</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aab2a218af47694f</t>
+          <t>https://www.indeed.com/viewjob?jk=d56ba0f8432c551e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HireBrick</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, XGBoost, S3, EC2, Redshift</t>
+          <t>RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42952c6c6822c7d1</t>
+          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Technical Solutions Architect II -- Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, AWS SageMaker, Redshift, BigQuery, Synapse, Apache Airflow, CI/CD, Git</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Git, Python, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c1844de534a454d</t>
+          <t>https://www.indeed.com/viewjob?jk=b728ef15f5db284e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gen AI Engineer - Generative AI Engineer - W2</t>
+          <t>Senior Data Engineer, AI Systems</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Teamware Solutions</t>
+          <t>Movable Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, CI/CD, Jenkins</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PySpark, Kafka, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f54a866bb4415f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer II - Mexico</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Soho Square Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, MLflow, Docker, Kubernetes, CI/CD, Git, Kafka, Power BI, Matplotlib</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304bfbbbc6fa58d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Solution Builder</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Kinesis, Docker, CI/CD, Terraform, Git, Snowflake, Kafka, MongoDB</t>
+          <t>LangChain, LLaMA, Prompt Engineering, BigQuery, AKS, Snowflake, Databricks, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766bf8c1056e06a</t>
+          <t>https://www.indeed.com/viewjob?jk=8944926097450bea</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,277 +706,277 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96a2863adf9faa0</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Applied Cloud and AI Engineer - Equities Cloud Platform Technology</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HireBrick</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89871434f1e9543a</t>
+          <t>https://www.indeed.com/viewjob?jk=2aab273b0fa7c656</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
+          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28164931f351fbab</t>
+          <t>https://www.indeed.com/viewjob?jk=8830ca9e9e02ec63</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
+          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df011591222734f</t>
+          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
+          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5abb66dbd101f</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
+          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f4ce82f7c13b19</t>
+          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Branson, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
+          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0805e2a946703b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Elizabethtown, KY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
+          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dce09b15abca9e</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer -W2/1099</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RSA Tech Group</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, LLaMA, Gemini, Prompt Engineering, S3, Redshift, Terraform, Redshift, Python</t>
+          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a406f8fe296870d</t>
+          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Systems Reliability Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>ERCOT/Electric Reliability Council of Texas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Taylor, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec5f74553bd33ff</t>
+          <t>https://www.indeed.com/viewjob?jk=fa009f1d9ad37c54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Associate Engineer, Site Reliability</t>
+          <t>Security Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Verint Systems Inc.</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Copilot, Data Lake, Snowflake, Databricks, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9358a51aac56a77b</t>
+          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Integration Platform Developer</t>
+          <t>Cursor Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22f587e12fdff403</t>
+          <t>https://www.indeed.com/viewjob?jk=42e65a6b198e2a84</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Edge</t>
+          <t>Full stack Developer (Java - React JS)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Kafka, PostgreSQL, MySQL, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Apache Airflow, CI/CD, Git, Snowflake, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=369dafbf8f945cbc</t>
+          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Edge</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Vantor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Kafka, PostgreSQL, MySQL, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, PostgreSQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e7526d8ca2a1f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d15da2aa0fbf340</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer I, MLOps (Python/Big Data)</t>
+          <t>Senior Software Implementation Engineer (Forward Deployed)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Reveal-Brainspace</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AWS SageMaker, PySpark, Kafka, Hadoop, Python, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917730a7c5496e21</t>
+          <t>https://www.indeed.com/viewjob?jk=12897d9793e47f00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Analytics Consulting</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TransUnion</t>
+          <t>NRC Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, A/B Testing</t>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afda3fdd466fc58e</t>
+          <t>https://www.indeed.com/viewjob?jk=477cf7419a6e9a03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Architect - GTM Systems</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>NRC Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f141c28a8188c378</t>
+          <t>https://www.indeed.com/viewjob?jk=5ad3cc3288ac3b02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Java Developer (Java-focused)</t>
+          <t>M365 Copilot Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mobilunity</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, Kafka, MySQL, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, CI/CD, GitHub Actions, Git, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966da7da9f101b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=f24285d40c312ef4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mule ESB Developer</t>
+          <t>M365 Copilot Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, CI/CD, GitHub Actions, Git, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,19 +1336,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794eb6cc5b859c21</t>
+          <t>https://www.indeed.com/viewjob?jk=d6773dd818392f07</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>M365 Copilot Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, CI/CD, GitHub Actions, Git, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=731574a8194af788</t>
+          <t>https://www.indeed.com/viewjob?jk=7c5eab3db9560e4c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI QA Engineer / AI Test Architect</t>
+          <t>Senior Data Scientist, Delivery</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Togal AI</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, XGBoost, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f23e1d27ba11b6f8</t>
+          <t>https://www.indeed.com/viewjob?jk=6b23c38d3ab6400a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT Software Development Engineer</t>
+          <t>LLM Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>t1 energy</t>
+          <t>iTemp</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, S3, Glue, Athena, Docker, CI/CD, Terraform, Git, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3058ed29473a19b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e165dc93aab1e2b5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Principle Cybersecurity Analyst - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Henry Ford Health</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, CI/CD, Git, Power BI, Python, R, Scala</t>
+          <t>RAG, Cortex, Docker, CI/CD, Git, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29388890120f69b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee626748142c9742</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer</t>
+          <t>Senior Database Engineer - Remote</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a75cedf85fed51d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b0320618fca689</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fulton Bank</t>
+          <t>Epicor Software</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Tableau, Power BI, MicroStrategy, Python, SQL, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,252 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d32392e1cd7f4a</t>
+          <t>https://www.indeed.com/viewjob?jk=56aa4639c839c3c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Machine Learning Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a39548e22f5fc1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Machine Learning Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8c9637969f2527d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Machine Learning Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af77c0b5e2229a47</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Machine Learning Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e22c62159e534138</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Machine Learning Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PrizePicks</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c8c57724044aa99</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (10387, 10388, 10389)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Extreme Networks</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, PySpark, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa365d79f0ecb662</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Scientist</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cotality</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Hadoop, Dask, Python, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc311cc3d8a4b28c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-04.xlsx
+++ b/daily_matches/job_matches_2026-08-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Technical Architect - Platform - Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL</t>
+          <t>RAG, S3, Glue, Redshift, GitHub Actions, Git, Redshift, PySpark, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56ba0f8432c551e</t>
+          <t>https://www.indeed.com/viewjob?jk=eece3ee32f7b1807</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MongoDB</t>
+          <t>Generative AI, RAG, Cortex, Apache Airflow, Terraform, Git, Snowflake, Tableau, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55af6783f46758f5</t>
+          <t>https://www.indeed.com/viewjob?jk=094a9593deead928</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Java Developer - (2-4 years) || USC/GC/H4EAD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Git, Python, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b728ef15f5db284e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8be0cfb256a99dc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI Systems</t>
+          <t>Java Developer - (2-4 years) || USC/GC/H4EAD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Movable Ink</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PySpark, Kafka, Python</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ee9658ab84208e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a42079cd056bca9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Developer - (2-4 years) || USC/GC/H4EAD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Soho Square Solutions</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, MongoDB, Python, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5d26bb3bad16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=049d0e8971034526</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Solution Builder</t>
+          <t>Java Developer - (2-4 years) || USC/GC/H4EAD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, LLaMA, Prompt Engineering, BigQuery, AKS, Snowflake, Databricks, BigQuery, Python, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8944926097450bea</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0815780fbd70a7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Developer - (2-4 years) || USC/GC/H4EAD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e5d6c0fdb9641b</t>
+          <t>https://www.indeed.com/viewjob?jk=b09125616e70625a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Applied Cloud and AI Engineer - Equities Cloud Platform Technology</t>
+          <t>Java Developer - (2-4 years) || USC/GC/H4EAD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aab273b0fa7c656</t>
+          <t>https://www.indeed.com/viewjob?jk=a6fed123c0336cd6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Developer - (2-4 years) || USC/GC/H4EAD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8830ca9e9e02ec63</t>
+          <t>https://www.indeed.com/viewjob?jk=6f73bac1d7dfa693</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93316469b8b0f71</t>
+          <t>https://www.indeed.com/viewjob?jk=00d473be59e3a41a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
+          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b659b7a6fbcb97</t>
+          <t>https://www.indeed.com/viewjob?jk=60f594743e815870</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Temporary - Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>American Cancer Society</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
+          <t>Data Scientist, RAG, Apache Airflow, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c4f023ed70d574</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ff2eb19376110f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Compliance - Applied AI/ML Data Scientist - Associate</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
+          <t>Data Scientist, RAG, Prompt Engineering, XGBoost, LightGBM, CatBoost, Git, Databricks, Tableau, Matplotlib</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d2bf7a77d4f3f57</t>
+          <t>https://www.indeed.com/viewjob?jk=12008038ae30291c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Platform &amp; Integration Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>McNees Wallace &amp; Nurick</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
+          <t>Redshift, BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Redshift, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1fcea33a073a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a5602722f179d9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
+          <t>RAG, Copilot, BigQuery, CI/CD, Terraform, Git, Snowflake, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27aab943b0526b8</t>
+          <t>https://www.indeed.com/viewjob?jk=544a28387d489008</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Systems Reliability Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ERCOT/Electric Reliability Council of Texas</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Taylor, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, BigQuery, CI/CD, Terraform, Git, Snowflake, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa009f1d9ad37c54</t>
+          <t>https://www.indeed.com/viewjob?jk=222b7902ae0ec8de</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Security Data Solutions Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, Snowflake, Databricks, Kafka, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd478651cfb5e453</t>
+          <t>https://www.indeed.com/viewjob?jk=9f78bb69ee2fd7d5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cursor Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, S3, Glue, Athena, Kinesis, Docker, Kubernetes, Terraform, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e65a6b198e2a84</t>
+          <t>https://www.indeed.com/viewjob?jk=0484dcbf21a2277c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full stack Developer (Java - React JS)</t>
+          <t>Sr Integrations Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Apache Airflow, CI/CD, Git, Snowflake, Python, R, Java, Scala</t>
+          <t>Copilot, Docker, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b817ba113453fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9015e3c7881e4a32</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Developer, Applied AI, Penguin Random House (Open to Remote)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vantor</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, PostgreSQL, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, FastAPI, Docker, CI/CD, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d15da2aa0fbf340</t>
+          <t>https://www.indeed.com/viewjob?jk=1712a21bb6ea4be2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Implementation Engineer (Forward Deployed)</t>
+          <t>Senior Data Analyst - AI &amp; Dermatology Claims Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Reveal-Brainspace</t>
+          <t>Advanced Dermatology and Cosmetic Surgery</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12897d9793e47f00</t>
+          <t>https://www.indeed.com/viewjob?jk=9af492765f4e635b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NRC Health</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
+          <t>RAG, Azure ML, Docker, Kubernetes, AKS, CI/CD, Terraform, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=477cf7419a6e9a03</t>
+          <t>https://www.indeed.com/viewjob?jk=758ccc46b70f28f0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NRC Health</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
+          <t>RAG, Azure ML, Docker, Kubernetes, AKS, CI/CD, Terraform, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad3cc3288ac3b02</t>
+          <t>https://www.indeed.com/viewjob?jk=9721baf3a7f2cc59</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M365 Copilot Software Engineer</t>
+          <t>Software Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, CI/CD, GitHub Actions, Git, SQL, R</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f24285d40c312ef4</t>
+          <t>https://www.indeed.com/viewjob?jk=faf8a622e358b496</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M365 Copilot Software Engineer</t>
+          <t>.NET Architect (AWS &amp; GenAI)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, CI/CD, GitHub Actions, Git, SQL, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, S3, Kubernetes, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6773dd818392f07</t>
+          <t>https://www.indeed.com/viewjob?jk=2da3bf45ec54aa87</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>M365 Copilot Software Engineer</t>
+          <t>Software Developer / AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>PARKWOOD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, CI/CD, GitHub Actions, Git, SQL, R</t>
+          <t>AI Engineer, Copilot, CI/CD, PostgreSQL, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5eab3db9560e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=d949c9152a256893</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Delivery</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Point Predictive</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+          <t>Kinesis, Snowflake, Kafka, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b23c38d3ab6400a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0fcfaa7f8219e3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LLM Data Engineer</t>
+          <t>Senior Specialty Software Engineer - AI Infrastructure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>iTemp</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Docker, CI/CD, Terraform, Git, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Kubernetes, Kafka, Power BI, Python, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e165dc93aab1e2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d41601c8e00e569b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Principle Cybersecurity Analyst - Remote</t>
+          <t>Senior Data Engineer (Wizards)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Monumental Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Docker, CI/CD, Git, Kafka, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Docker, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee626748142c9742</t>
+          <t>https://www.indeed.com/viewjob?jk=a5c25034b008c460</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Remote</t>
+          <t>Data Scientist - R&amp;D (AI/ML)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Vermeer Corporation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Ames, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b0320618fca689</t>
+          <t>https://www.indeed.com/viewjob?jk=9540e0d2a5c9994a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Epicor Software</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Tableau, Power BI, MicroStrategy, Python, SQL, R</t>
+          <t>RAG, CI/CD, Git, Kafka, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56aa4639c839c3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e59a0bf77d3143</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Machine Learning Platform Engineer</t>
+          <t>Software Engineer II - Test Automation Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,217 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a39548e22f5fc1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Machine Learning Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>PrizePicks</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9637969f2527d</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Machine Learning Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>PrizePicks</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af77c0b5e2229a47</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Machine Learning Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>PrizePicks</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e22c62159e534138</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Machine Learning Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>PrizePicks</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8c57724044aa99</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (10387, 10388, 10389)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Extreme Networks</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, PySpark, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa365d79f0ecb662</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Scientist</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Cotality</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Hadoop, Dask, Python, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc311cc3d8a4b28c</t>
+          <t>https://www.indeed.com/viewjob?jk=00989e5f3083c465</t>
         </is>
       </c>
     </row>
